--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_175_R18.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_175_R18.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4323</v>
+        <v>7.6141</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9488</v>
+        <v>5.1978</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4835</v>
+        <v>2.4163</v>
       </c>
       <c r="G2" t="n">
         <v>3.2061</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3706</v>
+        <v>0.5524</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3961</v>
+        <v>0.6451</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0255</v>
+        <v>-0.0927</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7676</v>
+        <v>7.5734</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4075</v>
+        <v>3.4822</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3601</v>
+        <v>4.0913</v>
       </c>
       <c r="G3" t="n">
         <v>4.9038</v>
@@ -688,13 +688,13 @@
         <v>3.7112</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0958</v>
+        <v>-0.0984</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1968</v>
+        <v>0.2715</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.101</v>
+        <v>-0.3699</v>
       </c>
       <c r="V3" t="n">
         <v>1.6083</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9046</v>
+        <v>5.8881</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7216</v>
+        <v>4.8396</v>
       </c>
       <c r="F4" t="n">
-        <v>1.183</v>
+        <v>1.0485</v>
       </c>
       <c r="G4" t="n">
         <v>3.4636</v>
@@ -766,13 +766,13 @@
         <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1801</v>
+        <v>-0.1966</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5816</v>
+        <v>-0.4637</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4015</v>
+        <v>0.2671</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3943</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9899</v>
+        <v>3.1661</v>
       </c>
       <c r="E5" t="n">
-        <v>1.814</v>
+        <v>2.1246</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1759</v>
+        <v>1.0415</v>
       </c>
       <c r="G5" t="n">
         <v>2.0078</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1265</v>
+        <v>0.3027</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2161</v>
+        <v>0.0944</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3427</v>
+        <v>0.2082</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5361</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3217</v>
+        <v>1.6995</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7482</v>
+        <v>1.0588</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5735</v>
+        <v>0.6407</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1097</v>
@@ -922,13 +922,13 @@
         <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0299</v>
+        <v>0.3479</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1221</v>
+        <v>0.4327</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.152</v>
+        <v>-0.0848</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3943</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5446</v>
+        <v>1.0067</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6786</v>
+        <v>1.1071</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.134</v>
+        <v>-0.1004</v>
       </c>
       <c r="G7" t="n">
         <v>1.1537</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2175</v>
+        <v>0.2447</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2003</v>
+        <v>0.2282</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0171</v>
+        <v>0.0165</v>
       </c>
       <c r="V7" t="n">
         <v>0.5361</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7249</v>
+        <v>-0.4896</v>
       </c>
       <c r="E8" t="n">
         <v>-2.2511</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5262</v>
+        <v>1.7614</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5004</v>
@@ -1078,13 +1078,13 @@
         <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9203</v>
+        <v>-0.6851</v>
       </c>
       <c r="T8" t="n">
         <v>-0.2908</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.3943</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7973</v>
+        <v>-1.2006</v>
       </c>
       <c r="E9" t="n">
         <v>-2.9858</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1884</v>
+        <v>1.7852</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0588</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6352</v>
+        <v>0.232</v>
       </c>
       <c r="T9" t="n">
         <v>-0.4323</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0675</v>
+        <v>0.6642</v>
       </c>
       <c r="V9" t="n">
         <v>0.3943</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9824</v>
+        <v>-2.1078</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1342</v>
+        <v>-1.6493</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8481</v>
+        <v>-0.4585</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.265</v>
+        <v>-1.492</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.144</v>
+        <v>-2.5125</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.121</v>
+        <v>1.0205</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.6965</v>
+        <v>-0.8129</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7863</v>
+        <v>-2.2582</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.9102</v>
+        <v>1.4453</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5684</v>
+        <v>-0.6791</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3577</v>
+        <v>-0.2543</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2108</v>
+        <v>-0.4248</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>3.0154</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8909</v>
+        <v>-0.6879</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5623</v>
+        <v>-0.5737</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3286</v>
+        <v>-0.1142</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.2166</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9828</v>
+        <v>-2.1676</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1211</v>
+        <v>-1.2522</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8618</v>
+        <v>-0.9154</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.492</v>
+        <v>-2.265</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5125</v>
+        <v>-1.144</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0205</v>
+        <v>-1.121</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8129</v>
+        <v>-1.6965</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2582</v>
+        <v>-0.7863</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4453</v>
+        <v>-0.9102</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6791</v>
+        <v>-0.5684</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2543</v>
+        <v>-0.3577</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4248</v>
+        <v>-0.2108</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.0154</v>
+        <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.563</v>
+        <v>0.7057</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0455</v>
+        <v>0.4443</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5175</v>
+        <v>0.2614</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W11" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3261</v>
+        <v>-2.905</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2605</v>
+        <v>-2.9066</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0655</v>
+        <v>0.0017</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3041</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>0.21</v>
+        <v>0.6311</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2082</v>
+        <v>0.1456</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4182</v>
+        <v>0.4854</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.8303</v>
+        <v>-4.3871</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0498</v>
+        <v>-5.8755</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2196</v>
+        <v>1.4884</v>
       </c>
       <c r="G13" t="n">
         <v>1.0489</v>
@@ -1468,13 +1468,13 @@
         <v>2.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3681</v>
+        <v>-0.1887</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7591</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.391</v>
+        <v>-0.1221</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.3169</v>
+        <v>13.6902</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5161999999999987</v>
+        <v>0.8895999999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>12.8008</v>
+        <v>12.8007</v>
       </c>
       <c r="G14" t="n">
         <v>6.053899999999997</v>
@@ -1546,16 +1546,16 @@
         <v>25.5148</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7863000000000001</v>
+        <v>1.1598</v>
       </c>
       <c r="T14" t="n">
-        <v>0.06159999999999977</v>
+        <v>0.4347</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7248999999999999</v>
+        <v>0.7248</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.6779000000000002</v>
       </c>
       <c r="W14" t="n">
         <v>9.539099999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.4283</v>
+        <v>6.6927</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6611</v>
+        <v>3.8354</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7672</v>
+        <v>2.8573</v>
       </c>
       <c r="G15" t="n">
         <v>5.1948</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8751</v>
+        <v>0.1395</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9006</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0255</v>
+        <v>0.0646</v>
       </c>
       <c r="V15" t="n">
         <v>2.2862</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9177</v>
+        <v>1.161</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7941</v>
+        <v>-0.0564</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1236</v>
+        <v>1.2174</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3425</v>
+        <v>0.3945</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6421</v>
+        <v>0.2137</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.9846</v>
+        <v>0.1808</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.3051</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8773</v>
+        <v>0.1211</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1975</v>
+        <v>0.184</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0223</v>
+        <v>0.0893</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7648</v>
+        <v>0.0926</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.7871</v>
+        <v>-0.0033</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8685</v>
+        <v>-0.3932</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3462</v>
+        <v>-0.3615</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5223</v>
+        <v>-0.0316</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4762</v>
+        <v>0.8562</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2923</v>
+        <v>0.6761</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7685</v>
+        <v>0.1801</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3945</v>
+        <v>-1.3425</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2137</v>
+        <v>1.6421</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1808</v>
+        <v>-2.9846</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3051</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1211</v>
+        <v>0.8773</v>
       </c>
       <c r="L17" t="n">
-        <v>0.184</v>
+        <v>-0.1975</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0893</v>
+        <v>-2.0223</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0926</v>
+        <v>0.7648</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0033</v>
+        <v>-2.7871</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.078</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5975</v>
+        <v>0.2282</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4806</v>
+        <v>0.5788</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1752</v>
+        <v>-0.0658</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0582</v>
+        <v>-0.2957</v>
       </c>
       <c r="F18" t="n">
-        <v>0.117</v>
+        <v>0.2299</v>
       </c>
       <c r="G18" t="n">
         <v>1.4852</v>
@@ -1858,13 +1858,13 @@
         <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>0.08169999999999999</v>
+        <v>-0.1592</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1221</v>
+        <v>-0.2317</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0404</v>
+        <v>0.0725</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1903</v>
+        <v>-1.2747</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.7909</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5174</v>
+        <v>-0.4838</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7879</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.51</v>
+        <v>0.4257</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2715</v>
+        <v>0.1535</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2385</v>
+        <v>0.2721</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8036</v>
+        <v>-1.6683</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5475</v>
+        <v>-1.5804</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2561</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6816</v>
+        <v>-0.9251</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1753</v>
+        <v>1.2832</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.857</v>
+        <v>-2.2083</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4233</v>
+        <v>0.5652</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3865</v>
+        <v>1.4018</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0368</v>
+        <v>-0.8366</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1049</v>
+        <v>-1.4903</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2112</v>
+        <v>-0.1186</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8938</v>
+        <v>-1.3717</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>2.3195</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1822</v>
+        <v>-0.0294</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4208</v>
+        <v>-0.1845</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7613</v>
+        <v>0.1551</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X20" t="n">
         <v>-1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5615</v>
+        <v>-2.0667</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7967</v>
+        <v>-0.6655</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7647</v>
+        <v>-1.4013</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7515</v>
+        <v>-1.6816</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1224</v>
+        <v>0.1753</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6291</v>
+        <v>-1.857</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5727</v>
+        <v>0.4233</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7863</v>
+        <v>0.3865</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7863</v>
+        <v>0.0368</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1788</v>
+        <v>-2.1049</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3361</v>
+        <v>-0.2112</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1573</v>
+        <v>-1.8938</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2016</v>
+        <v>0.919</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.224</v>
+        <v>0.3029</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0224</v>
+        <v>0.6161</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5757</v>
+        <v>-2.3677</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5099</v>
+        <v>-3.392</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9342</v>
+        <v>1.0242</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9816</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4033</v>
+        <v>0.6113</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1968</v>
+        <v>0.3148</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2065</v>
+        <v>0.2965</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9252</v>
+        <v>-2.5279</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0522</v>
+        <v>-1.7967</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8729</v>
+        <v>-0.7311</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9251</v>
+        <v>-1.7515</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2832</v>
+        <v>-1.1224</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.2083</v>
+        <v>-0.6291</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5652</v>
+        <v>-1.5727</v>
       </c>
       <c r="K23" t="n">
-        <v>1.4018</v>
+        <v>-0.7863</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.8366</v>
+        <v>-0.7863</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4903</v>
+        <v>-0.1788</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1186</v>
+        <v>-0.3361</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3717</v>
+        <v>0.1573</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.7112</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2863</v>
+        <v>-0.168</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6563</v>
+        <v>-0.224</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.63</v>
+        <v>0.056</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
       <c r="W23" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>-1.0722</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4567</v>
+        <v>-2.8667</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7414</v>
+        <v>-2.0995</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.7672</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.4717</v>
+        <v>1.4857</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3326</v>
+        <v>-0.2375</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.1391</v>
+        <v>1.7232</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.3922</v>
+        <v>1.9221</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1113</v>
+        <v>0.3529</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.5035</v>
+        <v>1.5692</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.0795</v>
+        <v>-0.4364</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4439</v>
+        <v>-0.5904</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.154</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6959</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0751</v>
+        <v>-0.4246</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1019</v>
+        <v>-0.3104</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0268</v>
+        <v>-0.1142</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3943</v>
+        <v>-1.6083</v>
       </c>
       <c r="W24" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.7501</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5122</v>
+        <v>-3.2036</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4534</v>
+        <v>-2.8594</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0589</v>
+        <v>-0.3442</v>
       </c>
       <c r="G25" t="n">
-        <v>1.4857</v>
+        <v>-4.4717</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2375</v>
+        <v>-0.3326</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7232</v>
+        <v>-4.1391</v>
       </c>
       <c r="J25" t="n">
-        <v>1.9221</v>
+        <v>-3.3922</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3529</v>
+        <v>0.1113</v>
       </c>
       <c r="L25" t="n">
-        <v>1.5692</v>
+        <v>-3.5035</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4364</v>
+        <v>-1.0795</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5904</v>
+        <v>-0.4439</v>
       </c>
       <c r="O25" t="n">
-        <v>0.154</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.7112</v>
+        <v>-1.3917</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0701</v>
+        <v>0.1779</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6642</v>
+        <v>-0.2199</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4059</v>
+        <v>0.3978</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.6083</v>
+        <v>0.3943</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.6083</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.289</v>
+        <v>-3.6263</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.2476</v>
+        <v>-3.7758</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.0414</v>
+        <v>0.1495</v>
       </c>
       <c r="G26" t="n">
         <v>-1.672</v>
@@ -2482,13 +2482,13 @@
         <v>2.5515</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9959</v>
+        <v>-0.3332</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7389</v>
+        <v>-0.2671</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.257</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V26" t="n">
         <v>0.9304</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-13.3168</v>
+        <v>-10.9578</v>
       </c>
       <c r="E27" t="n">
-        <v>-12.8005</v>
+        <v>-12.8008</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.5161</v>
+        <v>1.8429</v>
       </c>
       <c r="G27" t="n">
-        <v>-6.053700000000002</v>
+        <v>-6.0537</v>
       </c>
       <c r="H27" t="n">
         <v>8.132899999999999</v>
@@ -2533,13 +2533,13 @@
         <v>-14.1869</v>
       </c>
       <c r="J27" t="n">
-        <v>4.5776</v>
+        <v>4.577600000000001</v>
       </c>
       <c r="K27" t="n">
         <v>6.6364</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.058799999999999</v>
+        <v>-2.0588</v>
       </c>
       <c r="M27" t="n">
         <v>-10.6314</v>
@@ -2554,19 +2554,19 @@
         <v>-5.7987</v>
       </c>
       <c r="Q27" t="n">
-        <v>-25.51459999999999</v>
+        <v>-25.5146</v>
       </c>
       <c r="R27" t="n">
         <v>19.716</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.7862</v>
+        <v>1.5728</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.7248000000000001</v>
+        <v>-0.7248</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.06160000000000004</v>
+        <v>2.2976</v>
       </c>
       <c r="V27" t="n">
         <v>-0.6779000000000003</v>
